--- a/mapping/PDTD_DTM/Mapping_FCT_CLOS_EXCEPTION.xlsx
+++ b/mapping/PDTD_DTM/Mapping_FCT_CLOS_EXCEPTION.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -167,8 +167,16 @@
     </font>
     <font>
       <name val="Times New Roman"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
       <b val="1"/>
-      <color theme="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -239,7 +247,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -400,7 +408,10 @@
     <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -707,15 +718,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16"/>
   <cols>
     <col width="34.33203125" customWidth="1" style="19" min="1" max="1"/>
     <col width="19" customWidth="1" style="19" min="2" max="2"/>
     <col width="30.6640625" bestFit="1" customWidth="1" style="15" min="3" max="3"/>
-    <col width="36.6640625" bestFit="1" customWidth="1" style="16" min="4" max="4"/>
-    <col width="59.5" customWidth="1" style="19" min="5" max="5"/>
-    <col width="59.1640625" customWidth="1" style="16" min="6" max="6"/>
+    <col width="69.1640625" customWidth="1" style="16" min="4" max="4"/>
+    <col width="90.1640625" customWidth="1" style="19" min="5" max="5"/>
+    <col width="90.1640625" customWidth="1" style="16" min="6" max="6"/>
     <col width="9.1640625" customWidth="1" style="19" min="7" max="16384"/>
   </cols>
   <sheetData>
@@ -735,7 +746,6 @@
           <t>STG_FCT_CLOS_EXCEPTION AS A</t>
         </is>
       </c>
-      <c r="F1" s="52" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
@@ -753,7 +763,6 @@
           <t>REF_PHAN_LOAI_DDE AS B</t>
         </is>
       </c>
-      <c r="F2" s="52" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="21" t="inlineStr">
@@ -771,7 +780,6 @@
           <t>STG_FCT_CLOS_WORKSTEP_EVENT AS C</t>
         </is>
       </c>
-      <c r="F3" s="52" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
@@ -789,7 +797,6 @@
           <t>STG_DIM_CLOS_WORKSTEP_DECISION AS D</t>
         </is>
       </c>
-      <c r="F4" s="52" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="13" t="n"/>
@@ -798,7 +805,6 @@
           <t>STG_DIM_CLOS_EXCEPTION AS E2</t>
         </is>
       </c>
-      <c r="F5" s="52" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="13" t="n"/>
@@ -807,47 +813,38 @@
           <t>STG_DIM_CLOS_CUSTOMER AS F</t>
         </is>
       </c>
-      <c r="F6" s="52" t="n"/>
     </row>
     <row r="7" hidden="1">
       <c r="A7" s="13" t="n"/>
       <c r="E7" s="52" t="n"/>
-      <c r="F7" s="52" t="n"/>
     </row>
     <row r="8" hidden="1">
       <c r="A8" s="13" t="n"/>
       <c r="E8" s="52" t="n"/>
-      <c r="F8" s="53" t="n"/>
     </row>
     <row r="9" hidden="1">
       <c r="A9" s="13" t="n"/>
       <c r="E9" s="53" t="n"/>
-      <c r="F9" s="52" t="n"/>
     </row>
     <row r="10" hidden="1">
       <c r="A10" s="13" t="n"/>
       <c r="E10" s="53" t="n"/>
-      <c r="F10" s="52" t="n"/>
     </row>
     <row r="11" hidden="1">
       <c r="A11" s="13" t="n"/>
       <c r="E11" s="53" t="n"/>
-      <c r="F11" s="52" t="n"/>
     </row>
     <row r="12" hidden="1">
       <c r="A12" s="13" t="n"/>
       <c r="E12" s="53" t="n"/>
-      <c r="F12" s="52" t="n"/>
     </row>
     <row r="13" hidden="1">
       <c r="A13" s="13" t="n"/>
       <c r="E13" s="53" t="n"/>
-      <c r="F13" s="52" t="n"/>
     </row>
     <row r="14" hidden="1">
       <c r="A14" s="13" t="n"/>
       <c r="E14" s="53" t="n"/>
-      <c r="F14" s="53" t="n"/>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="1" t="inlineStr">
@@ -875,9 +872,8 @@
           <t>How to mapping CLOS</t>
         </is>
       </c>
-      <c r="F15" s="1" t="n"/>
-    </row>
-    <row r="16" ht="51" customHeight="1">
+    </row>
+    <row r="16">
       <c r="A16" s="6" t="n"/>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="7" t="n"/>
@@ -887,9 +883,8 @@
         </is>
       </c>
       <c r="E16" s="6" t="n"/>
-      <c r="F16" s="12" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1">
+    </row>
+    <row r="17" ht="30" customHeight="1">
       <c r="A17" s="28" t="inlineStr">
         <is>
           <t>DAYID</t>
@@ -905,19 +900,18 @@
           <t>Ngày dữ liệu</t>
         </is>
       </c>
-      <c r="D17" s="27" t="inlineStr">
+      <c r="D17" s="54" t="inlineStr">
         <is>
           <t>PK (1/2) — Driving: STG_FCT_CLOS_EXCEPTION. Ngày dữ liệu. Bê nguyên 1:1 từ SB_DWH (qua vùng chìa STG_DTM) cho các cột gốc</t>
         </is>
       </c>
-      <c r="E17" s="28" t="inlineStr">
+      <c r="E17" s="31" t="inlineStr">
         <is>
           <t>A.DAYID</t>
         </is>
       </c>
-      <c r="F17" s="28" t="n"/>
-    </row>
-    <row r="18" ht="15" customHeight="1">
+    </row>
+    <row r="18" ht="30" customHeight="1">
       <c r="A18" s="28" t="inlineStr">
         <is>
           <t>EXCEPTION_BK</t>
@@ -933,17 +927,16 @@
           <t>Khóa nghiệp vụ</t>
         </is>
       </c>
-      <c r="D18" s="27" t="inlineStr">
+      <c r="D18" s="54" t="inlineStr">
         <is>
           <t>PK (2/2) — khóa nghiệp vụ của dòng ngoại lệ, gộp WI_NAME+EXCEPTION_CATEGORY+RAISED_BY+RAISED_DATE_TIME</t>
         </is>
       </c>
-      <c r="E18" s="28" t="inlineStr">
+      <c r="E18" s="31" t="inlineStr">
         <is>
           <t>A.EXCEPTION_BK</t>
         </is>
       </c>
-      <c r="F18" s="28" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" s="28" t="inlineStr">
@@ -961,19 +954,18 @@
           <t>Khóa tới hồ sơ tín dụng</t>
         </is>
       </c>
-      <c r="D19" s="27" t="inlineStr">
+      <c r="D19" s="54" t="inlineStr">
         <is>
           <t>Khóa tới DIM_CLOS_APPLICATION</t>
         </is>
       </c>
-      <c r="E19" s="28" t="inlineStr">
+      <c r="E19" s="31" t="inlineStr">
         <is>
           <t>A.APPLICATION_SK</t>
         </is>
       </c>
-      <c r="F19" s="28" t="n"/>
-    </row>
-    <row r="20" ht="15" customFormat="1" customHeight="1" s="20">
+    </row>
+    <row r="20" ht="15" customHeight="1">
       <c r="A20" s="28" t="inlineStr">
         <is>
           <t>EXCEPTION_SK</t>
@@ -989,17 +981,16 @@
           <t>Khóa tới ngoại lệ</t>
         </is>
       </c>
-      <c r="D20" s="27" t="inlineStr">
+      <c r="D20" s="54" t="inlineStr">
         <is>
           <t>Khóa tới DIM_CLOS_EXCEPTION</t>
         </is>
       </c>
-      <c r="E20" s="28" t="inlineStr">
+      <c r="E20" s="31" t="inlineStr">
         <is>
           <t>A.EXCEPTION_SK</t>
         </is>
       </c>
-      <c r="F20" s="28" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="28" t="inlineStr">
@@ -1017,17 +1008,16 @@
           <t>Khóa tới người nêu lý do</t>
         </is>
       </c>
-      <c r="D21" s="27" t="inlineStr">
+      <c r="D21" s="54" t="inlineStr">
         <is>
           <t>Khóa tới DIM_LOS_USER, người nêu lý do</t>
         </is>
       </c>
-      <c r="E21" s="28" t="inlineStr">
+      <c r="E21" s="31" t="inlineStr">
         <is>
           <t>A.USER_SK</t>
         </is>
       </c>
-      <c r="F21" s="28" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" s="28" t="inlineStr">
@@ -1045,17 +1035,16 @@
           <t>Khóa tới khách hàng</t>
         </is>
       </c>
-      <c r="D22" s="27" t="inlineStr">
+      <c r="D22" s="54" t="inlineStr">
         <is>
           <t>Khóa tới DIM_CLOS_CUSTOMER</t>
         </is>
       </c>
-      <c r="E22" s="28" t="inlineStr">
+      <c r="E22" s="31" t="inlineStr">
         <is>
           <t>A.CUSTOMER_SK</t>
         </is>
       </c>
-      <c r="F22" s="28" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="28" t="inlineStr">
@@ -1073,17 +1062,16 @@
           <t>Mã hồ sơ tín dụng</t>
         </is>
       </c>
-      <c r="D23" s="27" t="inlineStr">
+      <c r="D23" s="54" t="inlineStr">
         <is>
           <t>Mã hồ sơ tín dụng CLOS</t>
         </is>
       </c>
-      <c r="E23" s="28" t="inlineStr">
+      <c r="E23" s="31" t="inlineStr">
         <is>
           <t>A.WI_NAME</t>
         </is>
       </c>
-      <c r="F23" s="28" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" s="28" t="inlineStr">
@@ -1101,17 +1089,16 @@
           <t>Phân nhóm nội dung</t>
         </is>
       </c>
-      <c r="D24" s="27" t="inlineStr">
+      <c r="D24" s="54" t="inlineStr">
         <is>
           <t>Phân nhóm nội dung cần làm rõ</t>
         </is>
       </c>
-      <c r="E24" s="28" t="inlineStr">
+      <c r="E24" s="31" t="inlineStr">
         <is>
           <t>A.EXCEPTION_CATEGORY</t>
         </is>
       </c>
-      <c r="F24" s="28" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" s="28" t="inlineStr">
@@ -1129,17 +1116,16 @@
           <t>Người nêu nội dung</t>
         </is>
       </c>
-      <c r="D25" s="27" t="inlineStr">
+      <c r="D25" s="54" t="inlineStr">
         <is>
           <t>Người nêu nội dung cần làm rõ</t>
         </is>
       </c>
-      <c r="E25" s="28" t="inlineStr">
+      <c r="E25" s="31" t="inlineStr">
         <is>
           <t>A.RAISED_BY</t>
         </is>
       </c>
-      <c r="F25" s="28" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="28" t="inlineStr">
@@ -1157,17 +1143,16 @@
           <t>Thời điểm nêu nội dung</t>
         </is>
       </c>
-      <c r="D26" s="27" t="inlineStr">
+      <c r="D26" s="54" t="inlineStr">
         <is>
           <t>Thời điểm nêu nội dung cần làm rõ</t>
         </is>
       </c>
-      <c r="E26" s="28" t="inlineStr">
+      <c r="E26" s="31" t="inlineStr">
         <is>
           <t>A.RAISED_DATE_TIME</t>
         </is>
       </c>
-      <c r="F26" s="28" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="28" t="inlineStr">
@@ -1185,17 +1170,16 @@
           <t>Tên nội dung cần làm rõ</t>
         </is>
       </c>
-      <c r="D27" s="27" t="inlineStr">
+      <c r="D27" s="54" t="inlineStr">
         <is>
           <t>Tên nội dung cần làm rõ</t>
         </is>
       </c>
-      <c r="E27" s="28" t="inlineStr">
+      <c r="E27" s="31" t="inlineStr">
         <is>
           <t>A.EXCEPTION_NAME</t>
         </is>
       </c>
-      <c r="F27" s="28" t="n"/>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="28" t="inlineStr">
@@ -1213,17 +1197,16 @@
           <t>Ghi chú</t>
         </is>
       </c>
-      <c r="D28" s="27" t="inlineStr">
+      <c r="D28" s="54" t="inlineStr">
         <is>
           <t>Ghi chú của nội dung cần làm rõ</t>
         </is>
       </c>
-      <c r="E28" s="28" t="inlineStr">
+      <c r="E28" s="31" t="inlineStr">
         <is>
           <t>A.EXCEPTION_REMARKS</t>
         </is>
       </c>
-      <c r="F28" s="28" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="28" t="inlineStr">
@@ -1241,19 +1224,18 @@
           <t>Loại ghi nhận</t>
         </is>
       </c>
-      <c r="D29" s="27" t="inlineStr">
+      <c r="D29" s="54" t="inlineStr">
         <is>
           <t>Loại ghi nhận, Raise hay Clear</t>
         </is>
       </c>
-      <c r="E29" s="28" t="inlineStr">
+      <c r="E29" s="31" t="inlineStr">
         <is>
           <t>A.RCTYPE</t>
         </is>
       </c>
-      <c r="F29" s="28" t="n"/>
-    </row>
-    <row r="30" ht="15" customHeight="1">
+    </row>
+    <row r="30" ht="45" customHeight="1">
       <c r="A30" s="28" t="inlineStr">
         <is>
           <t>PHAN_LOAI_DDE</t>
@@ -1269,19 +1251,18 @@
           <t>Phân loại nguyên nhân nhập liệu</t>
         </is>
       </c>
-      <c r="D30" s="27" t="inlineStr">
+      <c r="D30" s="54" t="inlineStr">
         <is>
           <t>Phân loại nguyên nhân trả về ở khâu nhập liệu. REF_PHAN_LOAI_DDE chỉ tồn tại vật lý ở PDTD_DTM (không có bản SB_DWH) — JOIN vào bảng REF_ là đặc quyền riêng của tầng PDTD_DTM</t>
         </is>
       </c>
-      <c r="E30" s="28" t="inlineStr">
+      <c r="E30" s="31" t="inlineStr">
         <is>
           <t>B.PHAN_LOAI_DDE</t>
         </is>
       </c>
-      <c r="F30" s="28" t="n"/>
-    </row>
-    <row r="31" ht="15" customHeight="1">
+    </row>
+    <row r="31" ht="600" customHeight="1">
       <c r="A31" s="28" t="inlineStr">
         <is>
           <t>CHECK_FTR</t>
@@ -1297,19 +1278,18 @@
           <t>Vi phạm First Time Right</t>
         </is>
       </c>
-      <c r="D31" s="27" t="inlineStr">
-        <is>
-          <t>Vi phạm nguyên tắc First Time Right — per-hồ-sơ (mọi dòng cùng WI_NAME phải cùng đạt điều kiện). [CẦN REVIEW] Logic SRS BC7 BR 1.2/1.3 rất dài (phân nhóm CUST_GROUP, tổ hợp ACTIVITYNAME+DECISION_CODE+EXCEPTION_CATEGORY cụ thể cho KHDN vs KHDNL/ĐT&amp;ĐCTC, EXISTS đối chiếu lịch sử xử lý) — giữ nguyên văn công thức từ LLD, không re-derive</t>
-        </is>
-      </c>
-      <c r="E31" s="28" t="inlineStr">
+      <c r="D31" s="54" t="inlineStr">
+        <is>
+          <t>Vi phạm nguyên tắc First Time Right — per-hồ-sơ (mọi dòng cùng WI_NAME phải cùng đạt điều kiện).2/1.3 rất dài (phân nhóm CUST_GROUP, tổ hợp ACTIVITYNAME+DECISION_CODE+EXCEPTION_CATEGORY cụ thể cho KHDN vs KHDNL/ĐT&amp;ĐCTC, EXISTS đối chiếu lịch sử xử lý) — giữ nguyên văn công thức từ LLD, không re-derive</t>
+        </is>
+      </c>
+      <c r="E31" s="31" t="inlineStr">
         <is>
           <t>CASE WHEN NOT EXISTS (SELECT 1 FROM A x LEFT JOIN E2 de ON de.DIMENSION_KEY = x.EXCEPTION_SK LEFT JOIN F kc ON kc.DIMENSION_KEY = x.CUSTOMER_SK WHERE x.WI_NAME = A.WI_NAME AND NOT ( ( (kc.CUST_GROUP IN ('MSME','SME','USME') AND ( (de.ACTIVITYNAME = 'DetailDataEntry' AND de.DECISION_CODE = 'Send_Back' AND (de.EXCEPTION_CATEGORY LIKE 'DE-BR-NEW: Chất lượng bản scan mờ không thấy thông tin - %' OR de.EXCEPTION_CATEGORY IN ('DE-BR-NEW: Bổ sung ý kiến tư vấn của bên thứ 3 (pháp chế, chính sách, sản phẩm, thẩm định,…)','DE-BR-NEW: Lỗi hệ thống (LOS, T24, XHTD,…)','DE-BR-NEW: Lỗi lựa chọn phân luồng, quy trình trên hệ thống'))) OR (de.ACTIVITYNAME = 'DataInputerChecker' AND de.DECISION_CODE = 'Additional_Doc_Required' AND (de.EXCEPTION_CATEGORY LIKE 'BC3-BR-NEW: Chất lượng bản scan mờ không thấy thông tin - %' OR de.EXCEPTION_CATEGORY IN ('BC3-BR-NEW: Bổ sung ý kiến tư vấn của bên thứ 3 (pháp chế, chính sách, sản phẩm, thẩm định,…)','BC3-BR-NEW: Lỗi hệ thống (LOS, T24, XHTD,…)'))) OR (de.ACTIVITYNAME = 'UnderwriterMaker' AND de.DECISION_CODE = 'Additional_Doc_Required' AND (de.EXCEPTION_CATEGORY LIKE '%UW-BR- FTR:Bổ sung hồ sơ%' OR de.EXCEPTION_CATEGORY IN ('UW-BR-FTR: bổ sung hồ sơ','UW-BR-FTR:Giải trình, làm rõ nội dung hồ sơ trường hợp các nội dung yêu cầu giải trình làm rõ ngoài HD thẩm định'))) OR (de.ACTIVITYNAME = 'UnderwriterMaker' AND de.DECISION_CODE = 'Send_Back to BranchSupport' AND de.EXCEPTION_CATEGORY = 'UW-BR: Gửi dự thảo đề xuất cho chi nhánh') )) OR (kc.CUST_GROUP IN ('FDI','SOC','JSC','NBFI','BANK','STR') AND ( (de.ACTIVITYNAME = 'DetailDataEntry' AND de.DECISION_CODE = 'Send_Back' AND (de.EXCEPTION_CATEGORY LIKE 'DE-BR-NEW: Chất lượng bản scan mờ không thấy thông tin - %' OR de.EXCEPTION_CATEGORY IN ('DE-BR-NEW: Bổ sung ý kiến tư vấn của bên thứ 3 (pháp chế, chính sách, sản phẩm, thẩm định,…)','DE-BR-NEW: Lỗi hệ thống (LOS, T24, XHTD,…)','DE-BR-NEW: Lỗi lựa chọn phân luồng, quy trình trên hệ thống'))) OR (de.ACTIVITYNAME = 'DataInputerChecker' AND de.DECISION_CODE = 'Additional_Doc_Required' AND (de.EXCEPTION_CATEGORY LIKE 'BC3-BR-NEW: Chất lượng bản scan mờ không thấy thông tin - %' OR de.EXCEPTION_CATEGORY IN ('BC3-BR-NEW: Bổ sung ý kiến tư vấn của bên thứ 3 (pháp chế, chính sách, sản phẩm, thẩm định,…)','BC3-BR-NEW: Lỗi hệ thống (LOS, T24, XHTD,…)'))) OR (de.ACTIVITYNAME = 'UnderwriterMaker' AND de.DECISION_CODE = 'Additional_Doc_Required' AND (de.EXCEPTION_CATEGORY LIKE '%UW-BR- FTR:Bổ sung hồ sơ%' OR de.EXCEPTION_CATEGORY IN ('UW-BR-FTR: bổ sung hồ sơ','UW-BR-FTR:Giải trình, làm rõ nội dung hồ sơ trường hợp các nội dung yêu cầu giải trình làm rõ ngoài HD thẩm định','UW-BR: Gửi dự thảo đề xuất cho chi nhánh'))) )) ) AND EXISTS (SELECT 1 FROM C we LEFT JOIN D wd ON wd.DIMENSION_KEY = we.WORKSTEP_DECISION_SK WHERE we.WI_NAME = x.WI_NAME AND wd.WORKSTEP_CODE = de.ACTIVITYNAME AND wd.DECISION_CODE = de.DECISION_CODE)) THEN 'First Time Right' ELSE 'Not First Time Right' END</t>
         </is>
       </c>
-      <c r="F31" s="28" t="n"/>
-    </row>
-    <row r="32" ht="15" customHeight="1">
+    </row>
+    <row r="32" ht="120" customHeight="1">
       <c r="A32" s="28" t="inlineStr">
         <is>
           <t>FIRST_WORKSTEP_RETURN</t>
@@ -1325,164 +1305,39 @@
           <t>Bước trả về đầu tiên</t>
         </is>
       </c>
-      <c r="D32" s="27" t="inlineStr">
+      <c r="D32" s="54" t="inlineStr">
         <is>
           <t>Bước xử lý phát sinh trả về đầu tiên. WORKSTEP_CODE của dòng có MIN(EXITDATE) theo WI_NAME (không phải DAYID — WE là nhật ký toàn bộ lịch sử, không snapshot theo ngày) thỏa 3 nhánh OR về WORKSTEP_CODE/DECISION_CODE. DECISION_CODE tra qua WORKSTEP_DECISION_SK → STG_DIM_CLOS_WORKSTEP_DECISION</t>
         </is>
       </c>
-      <c r="E32" s="28" t="inlineStr">
+      <c r="E32" s="31" t="inlineStr">
         <is>
           <t>(SELECT we.WORKSTEP_CODE FROM C we LEFT JOIN D wd ON wd.DIMENSION_KEY = we.WORKSTEP_DECISION_SK WHERE we.WI_NAME = A.WI_NAME AND we.EXITDATE IS NOT NULL AND ((we.WORKSTEP_CODE = 'DetailDataEntry' AND wd.DECISION_CODE = 'Send_Back') OR (we.WORKSTEP_CODE IN ('DataInputerChecker','UnderwriterMaker','CreditApproval') AND wd.DECISION_CODE = 'Additional_Doc_Required') OR (we.WORKSTEP_CODE = 'UnderwriterMaker' AND wd.DECISION_CODE = 'Send_Back to BranchSupport')) ORDER BY we.EXITDATE ASC FETCH FIRST 1 ROW ONLY)</t>
         </is>
       </c>
-      <c r="F32" s="28" t="n"/>
-    </row>
-    <row r="33" ht="34" customHeight="1"/>
+    </row>
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="10" t="n"/>
       <c r="B34" s="10" t="n"/>
       <c r="C34" s="10" t="n"/>
-      <c r="D34" s="54" t="inlineStr">
+      <c r="D34" s="55" t="inlineStr">
         <is>
           <t>Điều kiện join giữa các bảng</t>
         </is>
       </c>
       <c r="E34" s="10" t="n"/>
-      <c r="F34" s="10" t="n"/>
-    </row>
-    <row r="35" ht="45" customHeight="1">
+    </row>
+    <row r="35" ht="30" customHeight="1">
       <c r="A35" s="25" t="n"/>
       <c r="B35" s="25" t="n"/>
       <c r="C35" s="51" t="n"/>
-      <c r="D35" s="8" t="n"/>
+      <c r="D35" s="54" t="n"/>
       <c r="E35" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN B.EXCEPTION_CATEGORY = A.EXCEPTION_CATEGORY AND B.SYSTEMNAME = 'CLOS'</t>
         </is>
       </c>
-      <c r="F35" s="8" t="n"/>
-    </row>
-    <row r="36" ht="17" customHeight="1"/>
-    <row r="37" ht="51" customHeight="1"/>
-    <row r="38" ht="51" customHeight="1"/>
-    <row r="39" ht="34" customHeight="1"/>
-    <row r="40" ht="34" customHeight="1"/>
-    <row r="41" ht="34" customHeight="1"/>
-    <row r="42" ht="17" customHeight="1"/>
-    <row r="43" ht="34" customHeight="1"/>
-    <row r="44" ht="17" customHeight="1"/>
-    <row r="45" ht="85" customHeight="1"/>
-    <row r="46" ht="34" customHeight="1"/>
-    <row r="47" ht="17" customHeight="1"/>
-    <row r="48" ht="17" customHeight="1"/>
-    <row r="49" ht="17" customHeight="1"/>
-    <row r="50" ht="51" customHeight="1"/>
-    <row r="51" ht="51" customHeight="1"/>
-    <row r="52" ht="34" customHeight="1"/>
-    <row r="53" ht="34" customHeight="1"/>
-    <row r="54" ht="34" customHeight="1"/>
-    <row r="55" ht="34" customHeight="1"/>
-    <row r="56" ht="68" customHeight="1"/>
-    <row r="57" ht="51" customHeight="1"/>
-    <row r="58" ht="34" customHeight="1"/>
-    <row r="59" ht="17" customHeight="1"/>
-    <row r="60" ht="34" customHeight="1"/>
-    <row r="61" ht="17" customHeight="1"/>
-    <row r="62" ht="85" customHeight="1"/>
-    <row r="63" ht="85" customHeight="1"/>
-    <row r="64" ht="34" customHeight="1"/>
-    <row r="65" ht="17" customHeight="1"/>
-    <row r="66" ht="34" customHeight="1"/>
-    <row r="67" ht="51" customHeight="1"/>
-    <row r="68" ht="51" customHeight="1"/>
-    <row r="69" ht="51" customHeight="1"/>
-    <row r="70" ht="17" customHeight="1"/>
-    <row r="71" ht="34" customHeight="1"/>
-    <row r="72" ht="34" customHeight="1"/>
-    <row r="73" ht="34" customHeight="1"/>
-    <row r="74" ht="34" customHeight="1"/>
-    <row r="75" ht="34" customHeight="1"/>
-    <row r="76" ht="34" customHeight="1"/>
-    <row r="77" ht="51" customHeight="1"/>
-    <row r="78" ht="34" customHeight="1"/>
-    <row r="79" ht="51" customHeight="1"/>
-    <row r="80" ht="17" customHeight="1"/>
-    <row r="81" ht="17" customHeight="1"/>
-    <row r="82" ht="17" customHeight="1"/>
-    <row r="83" ht="17" customHeight="1"/>
-    <row r="84" ht="17" customHeight="1"/>
-    <row r="85" ht="17" customHeight="1"/>
-    <row r="86" ht="17" customHeight="1"/>
-    <row r="87" ht="17" customHeight="1"/>
-    <row r="88" ht="17" customHeight="1"/>
-    <row r="89" ht="17" customHeight="1"/>
-    <row r="90" ht="34" customHeight="1"/>
-    <row r="91" ht="17" customHeight="1"/>
-    <row r="92" ht="17" customHeight="1"/>
-    <row r="93" ht="17" customHeight="1"/>
-    <row r="94" ht="17" customHeight="1"/>
-    <row r="95" ht="17" customHeight="1"/>
-    <row r="96" ht="17" customHeight="1"/>
-    <row r="97" ht="17" customHeight="1"/>
-    <row r="100" ht="187" customHeight="1"/>
-    <row r="101" ht="17" customHeight="1"/>
-    <row r="102" ht="17" customHeight="1"/>
-    <row r="103" ht="17" customHeight="1"/>
-    <row r="104" ht="17" customHeight="1"/>
-    <row r="105" ht="17" customHeight="1"/>
-    <row r="106" ht="17" customHeight="1"/>
-    <row r="107" ht="17" customHeight="1"/>
-    <row r="108" ht="17" customHeight="1"/>
-    <row r="109" ht="17" customHeight="1"/>
-    <row r="110" ht="17" customHeight="1"/>
-    <row r="111" ht="17" customHeight="1"/>
-    <row r="112" ht="17" customHeight="1"/>
-    <row r="113" ht="17" customHeight="1"/>
-    <row r="114" ht="17" customHeight="1"/>
-    <row r="115" ht="17" customHeight="1"/>
-    <row r="116" ht="17" customHeight="1"/>
-    <row r="117" ht="17" customHeight="1"/>
-    <row r="118" ht="17" customHeight="1"/>
-    <row r="119" ht="17" customHeight="1"/>
-    <row r="120" ht="68" customHeight="1"/>
-    <row r="121" ht="51" customHeight="1"/>
-    <row r="122" ht="34" customHeight="1"/>
-    <row r="123" ht="153" customHeight="1"/>
-    <row r="124" ht="17" customHeight="1"/>
-    <row r="125" ht="17" customHeight="1"/>
-    <row r="132" ht="60" customHeight="1"/>
-    <row r="133" ht="17" customHeight="1"/>
-    <row r="134" ht="17" customHeight="1"/>
-    <row r="135" ht="17" customHeight="1"/>
-    <row r="136" ht="17" customHeight="1"/>
-    <row r="137" ht="51" customHeight="1"/>
-    <row r="138" ht="45" customHeight="1"/>
-    <row r="139" ht="120" customHeight="1"/>
-    <row r="141" ht="384" customHeight="1"/>
-    <row r="143" ht="34" customHeight="1"/>
-    <row r="148" ht="119" customHeight="1"/>
-    <row r="149" ht="17" customHeight="1"/>
-    <row r="150" ht="17" customHeight="1"/>
-    <row r="151" ht="17" customHeight="1"/>
-    <row r="152" ht="51" customHeight="1"/>
-    <row r="153" ht="34" customHeight="1"/>
-    <row r="154" ht="30" customHeight="1"/>
-    <row r="155" ht="17" customHeight="1"/>
-    <row r="157" ht="119" customHeight="1"/>
-    <row r="158" ht="17" customHeight="1"/>
-    <row r="159" ht="17" customHeight="1"/>
-    <row r="160" ht="17" customHeight="1"/>
-    <row r="161" ht="17" customHeight="1"/>
-    <row r="162" ht="17" customHeight="1"/>
-    <row r="163" ht="17" customHeight="1"/>
-    <row r="164" ht="17" customHeight="1"/>
-    <row r="165" ht="17" customHeight="1"/>
-    <row r="166" ht="34" customHeight="1"/>
-    <row r="167" ht="34" customHeight="1"/>
-    <row r="168" ht="16" customHeight="1"/>
-    <row r="169" ht="17" customHeight="1"/>
-    <row r="170" ht="17" customHeight="1"/>
-    <row r="2480" customFormat="1" s="19"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/mapping/PDTD_DTM/Mapping_FCT_CLOS_EXCEPTION.xlsx
+++ b/mapping/PDTD_DTM/Mapping_FCT_CLOS_EXCEPTION.xlsx
@@ -718,7 +718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16"/>
   <cols>
     <col width="34.33203125" customWidth="1" style="19" min="1" max="1"/>
@@ -755,12 +755,12 @@
       </c>
       <c r="B2" s="19" t="inlineStr">
         <is>
-          <t>Relay 1:1 từ STG_DTM.STG_FCT_CLOS_EXCEPTION sang PDTD_DTM, bổ sung PHAN_LOAI_DDE/CHECK_FTR/FIRST_WORKSTEP_RETURN</t>
+          <t>Bảng FACT chi tiết tại PDTD_DTM, bê nguyên 1:1 từ STG_DTM.STG_FCT_CLOS_EXCEPTION, bổ sung 3 cột phái sinh CHECK_FTR/FIRST_WORKSTEP_RETURN/PHAN_LOAI_DDE</t>
         </is>
       </c>
       <c r="E2" s="52" t="inlineStr">
         <is>
-          <t>REF_PHAN_LOAI_DDE AS B</t>
+          <t>STG_FCT_CLOS_WORKSTEP_EVENT AS B</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="E3" s="52" t="inlineStr">
         <is>
-          <t>STG_FCT_CLOS_WORKSTEP_EVENT AS C</t>
+          <t>REF_PHAN_LOAI_DDE AS C</t>
         </is>
       </c>
     </row>
@@ -792,27 +792,15 @@
           <t>Chạy dữ liệu FULL hàng ngày</t>
         </is>
       </c>
-      <c r="E4" s="52" t="inlineStr">
-        <is>
-          <t>STG_DIM_CLOS_WORKSTEP_DECISION AS D</t>
-        </is>
-      </c>
+      <c r="E4" s="52" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="13" t="n"/>
-      <c r="E5" s="52" t="inlineStr">
-        <is>
-          <t>STG_DIM_CLOS_EXCEPTION AS E2</t>
-        </is>
-      </c>
+      <c r="E5" s="52" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="13" t="n"/>
-      <c r="E6" s="52" t="inlineStr">
-        <is>
-          <t>STG_DIM_CLOS_CUSTOMER AS F</t>
-        </is>
-      </c>
+      <c r="E6" s="52" t="n"/>
     </row>
     <row r="7" hidden="1">
       <c r="A7" s="13" t="n"/>
@@ -902,7 +890,7 @@
       </c>
       <c r="D17" s="54" t="inlineStr">
         <is>
-          <t>PK (1/2) — Driving: STG_FCT_CLOS_EXCEPTION. Ngày dữ liệu. Bê nguyên 1:1 từ SB_DWH (qua vùng chìa STG_DTM) cho các cột gốc</t>
+          <t>Ngày dữ liệu. Bê nguyên 1:1 từ SB_DWH (qua vùng chìa STG_DTM) cho các cột gốc.</t>
         </is>
       </c>
       <c r="E17" s="31" t="inlineStr">
@@ -924,12 +912,12 @@
       </c>
       <c r="C18" s="26" t="inlineStr">
         <is>
-          <t>Khóa nghiệp vụ</t>
+          <t>Khóa nghiệp vụ dòng ngoại lệ</t>
         </is>
       </c>
       <c r="D18" s="54" t="inlineStr">
         <is>
-          <t>PK (2/2) — khóa nghiệp vụ của dòng ngoại lệ, gộp WI_NAME+EXCEPTION_CATEGORY+RAISED_BY+RAISED_DATE_TIME</t>
+          <t>Khóa nghiệp vụ của dòng ngoại lệ, gộp WI_NAME+EXCEPTION_CATEGORY+RAISED_BY+RAISED_DATE_TIME</t>
         </is>
       </c>
       <c r="E18" s="31" t="inlineStr">
@@ -951,7 +939,7 @@
       </c>
       <c r="C19" s="26" t="inlineStr">
         <is>
-          <t>Khóa tới hồ sơ tín dụng</t>
+          <t>Khóa hồ sơ tín dụng</t>
         </is>
       </c>
       <c r="D19" s="54" t="inlineStr">
@@ -965,37 +953,37 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
+    <row r="20" ht="30" customHeight="1">
       <c r="A20" s="28" t="inlineStr">
         <is>
-          <t>EXCEPTION_SK</t>
+          <t>WI_NAME</t>
         </is>
       </c>
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>VARCHAR2(100)</t>
         </is>
       </c>
       <c r="C20" s="26" t="inlineStr">
         <is>
-          <t>Khóa tới ngoại lệ</t>
+          <t>Mã hồ sơ tín dụng</t>
         </is>
       </c>
       <c r="D20" s="54" t="inlineStr">
         <is>
-          <t>Khóa tới DIM_CLOS_EXCEPTION</t>
+          <t>Mã hồ sơ tín dụng CLOS. Vị trí liền sau APPLICATION_SK, đồng bộ thứ tự với HLD mục 6.3.</t>
         </is>
       </c>
       <c r="E20" s="31" t="inlineStr">
         <is>
-          <t>A.EXCEPTION_SK</t>
+          <t>A.WI_NAME</t>
         </is>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="28" t="inlineStr">
         <is>
-          <t>USER_SK</t>
+          <t>EXCEPTION_SK</t>
         </is>
       </c>
       <c r="B21" s="25" t="inlineStr">
@@ -1005,336 +993,444 @@
       </c>
       <c r="C21" s="26" t="inlineStr">
         <is>
-          <t>Khóa tới người nêu lý do</t>
+          <t>Khóa ngoại lệ</t>
         </is>
       </c>
       <c r="D21" s="54" t="inlineStr">
         <is>
-          <t>Khóa tới DIM_LOS_USER, người nêu lý do</t>
+          <t>Khóa tới DIM_CLOS_EXCEPTION</t>
         </is>
       </c>
       <c r="E21" s="31" t="inlineStr">
         <is>
-          <t>A.USER_SK</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
+          <t>A.EXCEPTION_SK</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="60" customHeight="1">
       <c r="A22" s="28" t="inlineStr">
         <is>
-          <t>CUSTOMER_SK</t>
+          <t>WORKSTEP_CODE</t>
         </is>
       </c>
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>VARCHAR2(200)</t>
         </is>
       </c>
       <c r="C22" s="26" t="inlineStr">
         <is>
-          <t>Khóa tới khách hàng</t>
+          <t>Mã bước xử lý ngoại lệ</t>
         </is>
       </c>
       <c r="D22" s="54" t="inlineStr">
         <is>
-          <t>Khóa tới DIM_CLOS_CUSTOMER</t>
+          <t>CỘT MỚI — BK cạnh SK, tương ứng ACTIVITYNAME của dòng DIM_CLOS_EXCEPTION đã khớp EXCEPTION_SK. Bê 1:1 từ SB_DWH (qua vùng chìa STG_DTM) — giá trị đã có sẵn trong bước lọc EXISTS tại SB_DWH, phục vụ truy vết/đối soát BK không qua DIM.</t>
         </is>
       </c>
       <c r="E22" s="31" t="inlineStr">
         <is>
-          <t>A.CUSTOMER_SK</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
+          <t>A.WORKSTEP_CODE</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1">
       <c r="A23" s="28" t="inlineStr">
         <is>
-          <t>WI_NAME</t>
+          <t>DECISION_CODE</t>
         </is>
       </c>
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(100)</t>
+          <t>VARCHAR2(200)</t>
         </is>
       </c>
       <c r="C23" s="26" t="inlineStr">
         <is>
-          <t>Mã hồ sơ tín dụng</t>
+          <t>Mã quyết định ngoại lệ</t>
         </is>
       </c>
       <c r="D23" s="54" t="inlineStr">
         <is>
-          <t>Mã hồ sơ tín dụng CLOS</t>
+          <t>CỘT MỚI — nửa còn lại BK composite của DIM_CLOS_EXCEPTION ứng với dòng đã khớp EXCEPTION_SK. Bê 1:1 từ SB_DWH (qua vùng chìa STG_DTM) — giá trị đã có sẵn trong bước lọc EXISTS tại SB_DWH, phục vụ truy vết/đối soát BK không qua DIM.</t>
         </is>
       </c>
       <c r="E23" s="31" t="inlineStr">
         <is>
-          <t>A.WI_NAME</t>
+          <t>A.DECISION_CODE</t>
         </is>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" s="28" t="inlineStr">
         <is>
-          <t>EXCEPTION_CATEGORY</t>
+          <t>USER_SK</t>
         </is>
       </c>
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(500)</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="C24" s="26" t="inlineStr">
         <is>
-          <t>Phân nhóm nội dung</t>
+          <t>Khóa người nêu lý do</t>
         </is>
       </c>
       <c r="D24" s="54" t="inlineStr">
         <is>
-          <t>Phân nhóm nội dung cần làm rõ</t>
+          <t>Khóa tới DIM_LOS_USER, người nêu lý do</t>
         </is>
       </c>
       <c r="E24" s="31" t="inlineStr">
         <is>
-          <t>A.EXCEPTION_CATEGORY</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
+          <t>A.USER_SK</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="60" customHeight="1">
       <c r="A25" s="28" t="inlineStr">
         <is>
-          <t>RAISED_BY</t>
+          <t>USERNAME</t>
         </is>
       </c>
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(100)</t>
+          <t>VARCHAR2(150)</t>
         </is>
       </c>
       <c r="C25" s="26" t="inlineStr">
         <is>
-          <t>Người nêu nội dung</t>
+          <t>Tên tài khoản người nêu</t>
         </is>
       </c>
       <c r="D25" s="54" t="inlineStr">
         <is>
-          <t>Người nêu nội dung cần làm rõ</t>
+          <t>CỘT MỚI — BK cạnh SK, tên tài khoản dùng để lookup USER_SK. Bê 1:1 từ SB_DWH (qua vùng chìa STG_DTM), nguồn gốc xa NG_SB_CLOS_EXCEPTION.RAISED_BY — khác RAISED_BY (cột nghiệp vụ hiển thị), giữ tách biệt ý nghĩa khóa nghiệp vụ.</t>
         </is>
       </c>
       <c r="E25" s="31" t="inlineStr">
         <is>
-          <t>A.RAISED_BY</t>
+          <t>A.USERNAME</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="28" t="inlineStr">
         <is>
-          <t>RAISED_DATE_TIME</t>
+          <t>CUSTOMER_SK</t>
         </is>
       </c>
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="C26" s="26" t="inlineStr">
         <is>
-          <t>Thời điểm nêu nội dung</t>
+          <t>Khóa khách hàng</t>
         </is>
       </c>
       <c r="D26" s="54" t="inlineStr">
         <is>
-          <t>Thời điểm nêu nội dung cần làm rõ</t>
+          <t>Khóa tới DIM_CLOS_CUSTOMER</t>
         </is>
       </c>
       <c r="E26" s="31" t="inlineStr">
         <is>
-          <t>A.RAISED_DATE_TIME</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
+          <t>A.CUSTOMER_SK</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="45" customHeight="1">
       <c r="A27" s="28" t="inlineStr">
         <is>
-          <t>EXCEPTION_NAME</t>
+          <t>CUSTOMER_CODE</t>
         </is>
       </c>
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(500)</t>
+          <t>VARCHAR2(100)</t>
         </is>
       </c>
       <c r="C27" s="26" t="inlineStr">
         <is>
-          <t>Tên nội dung cần làm rõ</t>
+          <t>Mã khách hàng</t>
         </is>
       </c>
       <c r="D27" s="54" t="inlineStr">
         <is>
-          <t>Tên nội dung cần làm rõ</t>
+          <t>CỘT MỚI — BK cạnh SK, giá trị đã tra ra trong bước lookup CUSTOMER_SK. Bê 1:1 từ SB_DWH (qua vùng chìa STG_DTM), phục vụ truy vết/đối soát BK không qua DIM.</t>
         </is>
       </c>
       <c r="E27" s="31" t="inlineStr">
         <is>
-          <t>A.EXCEPTION_NAME</t>
+          <t>A.CUSTOMER_CODE</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="28" t="inlineStr">
         <is>
-          <t>EXCEPTION_REMARKS</t>
+          <t>EXCEPTION_CATEGORY</t>
         </is>
       </c>
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(4000)</t>
+          <t>VARCHAR2(500)</t>
         </is>
       </c>
       <c r="C28" s="26" t="inlineStr">
         <is>
-          <t>Ghi chú</t>
+          <t>Phân nhóm nội dung</t>
         </is>
       </c>
       <c r="D28" s="54" t="inlineStr">
         <is>
-          <t>Ghi chú của nội dung cần làm rõ</t>
+          <t>Phân nhóm nội dung cần làm rõ</t>
         </is>
       </c>
       <c r="E28" s="31" t="inlineStr">
         <is>
-          <t>A.EXCEPTION_REMARKS</t>
+          <t>A.EXCEPTION_CATEGORY</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="28" t="inlineStr">
         <is>
+          <t>RAISED_BY</t>
+        </is>
+      </c>
+      <c r="B29" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(100)</t>
+        </is>
+      </c>
+      <c r="C29" s="26" t="inlineStr">
+        <is>
+          <t>Người nêu lý do</t>
+        </is>
+      </c>
+      <c r="D29" s="54" t="inlineStr">
+        <is>
+          <t>Người nêu nội dung cần làm rõ</t>
+        </is>
+      </c>
+      <c r="E29" s="31" t="inlineStr">
+        <is>
+          <t>A.RAISED_BY</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="28" t="inlineStr">
+        <is>
+          <t>RAISED_DATE_TIME</t>
+        </is>
+      </c>
+      <c r="B30" s="25" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="C30" s="26" t="inlineStr">
+        <is>
+          <t>Thời điểm nêu lý do</t>
+        </is>
+      </c>
+      <c r="D30" s="54" t="inlineStr">
+        <is>
+          <t>Thời điểm nêu nội dung cần làm rõ</t>
+        </is>
+      </c>
+      <c r="E30" s="31" t="inlineStr">
+        <is>
+          <t>A.RAISED_DATE_TIME</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="28" t="inlineStr">
+        <is>
+          <t>EXCEPTION_NAME</t>
+        </is>
+      </c>
+      <c r="B31" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(500)</t>
+        </is>
+      </c>
+      <c r="C31" s="26" t="inlineStr">
+        <is>
+          <t>Tên nội dung ngoại lệ</t>
+        </is>
+      </c>
+      <c r="D31" s="54" t="inlineStr">
+        <is>
+          <t>Tên nội dung cần làm rõ</t>
+        </is>
+      </c>
+      <c r="E31" s="31" t="inlineStr">
+        <is>
+          <t>A.EXCEPTION_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="28" t="inlineStr">
+        <is>
+          <t>EXCEPTION_REMARKS</t>
+        </is>
+      </c>
+      <c r="B32" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(4000)</t>
+        </is>
+      </c>
+      <c r="C32" s="26" t="inlineStr">
+        <is>
+          <t>Ghi chú ngoại lệ</t>
+        </is>
+      </c>
+      <c r="D32" s="54" t="inlineStr">
+        <is>
+          <t>Ghi chú của nội dung cần làm rõ</t>
+        </is>
+      </c>
+      <c r="E32" s="31" t="inlineStr">
+        <is>
+          <t>A.EXCEPTION_REMARKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" s="28" t="inlineStr">
+        <is>
           <t>RCTYPE</t>
         </is>
       </c>
-      <c r="B29" s="25" t="inlineStr">
+      <c r="B33" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(20)</t>
         </is>
       </c>
-      <c r="C29" s="26" t="inlineStr">
+      <c r="C33" s="26" t="inlineStr">
         <is>
           <t>Loại ghi nhận</t>
         </is>
       </c>
-      <c r="D29" s="54" t="inlineStr">
+      <c r="D33" s="54" t="inlineStr">
         <is>
           <t>Loại ghi nhận, Raise hay Clear</t>
         </is>
       </c>
-      <c r="E29" s="31" t="inlineStr">
+      <c r="E33" s="31" t="inlineStr">
         <is>
           <t>A.RCTYPE</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="45" customHeight="1">
-      <c r="A30" s="28" t="inlineStr">
+    <row r="34" ht="285" customHeight="1">
+      <c r="A34" s="28" t="inlineStr">
+        <is>
+          <t>CHECK_FTR</t>
+        </is>
+      </c>
+      <c r="B34" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(20)</t>
+        </is>
+      </c>
+      <c r="C34" s="26" t="inlineStr">
+        <is>
+          <t>Vi phạm First Time Right</t>
+        </is>
+      </c>
+      <c r="D34" s="54" t="inlineStr">
+        <is>
+          <t>Vi phạm nguyên tắc First Time Right — per-hồ-sơ (mọi dòng cùng WI_NAME phải cùng đạt điều kiện). Đọc nguyên văn SRS BC7 BR 1.2/1.3 bảng T8 row 12 'CHECK_FTR' nhánh CLOS: logic SRS định nghĩa 'trường hợp NGOẠI LỆ hợp lệ' theo tổ hợp ACTIVITYNAME+DECISION_CODE+EXCEPTION_CATEGORY cụ thể, phân theo CUST_GROUP (KHDN/KHDNL), và tổ hợp WORKSTEP/DECISION đó phải thực sự tồn tại trong lịch sử xử lý (EXISTS STG_FCT_CLOS_WORKSTEP_EVENT).</t>
+        </is>
+      </c>
+      <c r="E34" s="31" t="inlineStr">
+        <is>
+          <t>CASE WHEN NOT EXISTS (SELECT 1 FROM STG_FCT_CLOS_EXCEPTION x LEFT JOIN STG_DIM_CLOS_EXCEPTION de ON de.DIMENSION_KEY = x.EXCEPTION_SK LEFT JOIN STG_DIM_CLOS_CUSTOMER kc ON kc.DIMENSION_KEY = x.CUSTOMER_SK WHERE x.WI_NAME = A.WI_NAME AND NOT ( ( (kc.CUST_GROUP IN ('MSME','SME','USME') AND ( (de.ACTIVITYNAME = 'DetailDataEntry' AND de.DECISION_CODE = 'Send_Back' AND (de.EXCEPTION_CATEGORY LIKE 'DE-BR-NEW: ...' OR de.EXCEPTION_CATEGORY IN (...))) OR (de.ACTIVITYNAME = 'DataInputerChecker' AND de.DECISION_CODE = 'Additional_Doc_Required' AND (...)) OR (de.ACTIVITYNAME = 'UnderwriterMaker' AND de.DECISION_CODE = 'Additional_Doc_Required' AND (...)) OR (de.ACTIVITYNAME = 'UnderwriterMaker' AND de.DECISION_CODE = 'Send_Back to BranchSupport' AND de.EXCEPTION_CATEGORY = 'UW-BR: Gửi dự thảo đề xuất cho chi nhánh') )) OR (kc.CUST_GROUP IN ('FDI','SOC','JSC','NBFI','BANK','STR') AND (...cùng 3 tổ hợp đầu, không có tổ hợp Send_Back to BranchSupport riêng...)) ) ) AND EXISTS (SELECT 1 FROM STG_FCT_CLOS_WORKSTEP_EVENT we LEFT JOIN STG_DIM_CLOS_WORKSTEP_DECISION wd ON wd.DIMENSION_KEY = we.WORKSTEP_DECISION_SK WHERE we.WI_NAME = x.WI_NAME AND wd.WORKSTEP_CODE = de.ACTIVITYNAME AND wd.DECISION_CODE = de.DECISION_CODE)) THEN 'First Time Right' ELSE 'Not First Time Right' END</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="135" customHeight="1">
+      <c r="A35" s="28" t="inlineStr">
+        <is>
+          <t>FIRST_WORKSTEP_RETURN</t>
+        </is>
+      </c>
+      <c r="B35" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(200)</t>
+        </is>
+      </c>
+      <c r="C35" s="26" t="inlineStr">
+        <is>
+          <t>Bước trả về đầu tiên</t>
+        </is>
+      </c>
+      <c r="D35" s="54" t="inlineStr">
+        <is>
+          <t>Bước xử lý phát sinh trả về đầu tiên. WORKSTEP_CODE của dòng có MIN(EXITDATE) theo WI_NAME (không phải DAYID — WE là nhật ký toàn bộ lịch sử, không snapshot theo ngày) thỏa 3 nhánh OR về WORKSTEP_CODE/DECISION_CODE. DECISION_CODE tra qua WORKSTEP_DECISION_SK → STG_DIM_CLOS_WORKSTEP_DECISION (đi qua vùng chìa STG_DTM; WE không denormalize DECISION_CODE).</t>
+        </is>
+      </c>
+      <c r="E35" s="31" t="inlineStr">
+        <is>
+          <t>(SELECT we.WORKSTEP_CODE FROM STG_FCT_CLOS_WORKSTEP_EVENT we LEFT JOIN STG_DIM_CLOS_WORKSTEP_DECISION wd ON wd.DIMENSION_KEY = we.WORKSTEP_DECISION_SK WHERE we.WI_NAME = A.WI_NAME AND we.EXITDATE IS NOT NULL AND ((we.WORKSTEP_CODE = 'DetailDataEntry' AND wd.DECISION_CODE = 'Send_Back') OR (we.WORKSTEP_CODE IN ('DataInputerChecker','UnderwriterMaker','CreditApproval') AND wd.DECISION_CODE = 'Additional_Doc_Required') OR (we.WORKSTEP_CODE = 'UnderwriterMaker' AND wd.DECISION_CODE = 'Send_Back to BranchSupport')) ORDER BY we.EXITDATE ASC FETCH FIRST 1 ROW ONLY)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="45" customHeight="1">
+      <c r="A36" s="28" t="inlineStr">
         <is>
           <t>PHAN_LOAI_DDE</t>
         </is>
       </c>
-      <c r="B30" s="25" t="inlineStr">
+      <c r="B36" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C30" s="26" t="inlineStr">
-        <is>
-          <t>Phân loại nguyên nhân nhập liệu</t>
-        </is>
-      </c>
-      <c r="D30" s="54" t="inlineStr">
-        <is>
-          <t>Phân loại nguyên nhân trả về ở khâu nhập liệu. REF_PHAN_LOAI_DDE chỉ tồn tại vật lý ở PDTD_DTM (không có bản SB_DWH) — JOIN vào bảng REF_ là đặc quyền riêng của tầng PDTD_DTM</t>
-        </is>
-      </c>
-      <c r="E30" s="31" t="inlineStr">
-        <is>
-          <t>B.PHAN_LOAI_DDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="600" customHeight="1">
-      <c r="A31" s="28" t="inlineStr">
-        <is>
-          <t>CHECK_FTR</t>
-        </is>
-      </c>
-      <c r="B31" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(20)</t>
-        </is>
-      </c>
-      <c r="C31" s="26" t="inlineStr">
-        <is>
-          <t>Vi phạm First Time Right</t>
-        </is>
-      </c>
-      <c r="D31" s="54" t="inlineStr">
-        <is>
-          <t>Vi phạm nguyên tắc First Time Right — per-hồ-sơ (mọi dòng cùng WI_NAME phải cùng đạt điều kiện).2/1.3 rất dài (phân nhóm CUST_GROUP, tổ hợp ACTIVITYNAME+DECISION_CODE+EXCEPTION_CATEGORY cụ thể cho KHDN vs KHDNL/ĐT&amp;ĐCTC, EXISTS đối chiếu lịch sử xử lý) — giữ nguyên văn công thức từ LLD, không re-derive</t>
-        </is>
-      </c>
-      <c r="E31" s="31" t="inlineStr">
-        <is>
-          <t>CASE WHEN NOT EXISTS (SELECT 1 FROM A x LEFT JOIN E2 de ON de.DIMENSION_KEY = x.EXCEPTION_SK LEFT JOIN F kc ON kc.DIMENSION_KEY = x.CUSTOMER_SK WHERE x.WI_NAME = A.WI_NAME AND NOT ( ( (kc.CUST_GROUP IN ('MSME','SME','USME') AND ( (de.ACTIVITYNAME = 'DetailDataEntry' AND de.DECISION_CODE = 'Send_Back' AND (de.EXCEPTION_CATEGORY LIKE 'DE-BR-NEW: Chất lượng bản scan mờ không thấy thông tin - %' OR de.EXCEPTION_CATEGORY IN ('DE-BR-NEW: Bổ sung ý kiến tư vấn của bên thứ 3 (pháp chế, chính sách, sản phẩm, thẩm định,…)','DE-BR-NEW: Lỗi hệ thống (LOS, T24, XHTD,…)','DE-BR-NEW: Lỗi lựa chọn phân luồng, quy trình trên hệ thống'))) OR (de.ACTIVITYNAME = 'DataInputerChecker' AND de.DECISION_CODE = 'Additional_Doc_Required' AND (de.EXCEPTION_CATEGORY LIKE 'BC3-BR-NEW: Chất lượng bản scan mờ không thấy thông tin - %' OR de.EXCEPTION_CATEGORY IN ('BC3-BR-NEW: Bổ sung ý kiến tư vấn của bên thứ 3 (pháp chế, chính sách, sản phẩm, thẩm định,…)','BC3-BR-NEW: Lỗi hệ thống (LOS, T24, XHTD,…)'))) OR (de.ACTIVITYNAME = 'UnderwriterMaker' AND de.DECISION_CODE = 'Additional_Doc_Required' AND (de.EXCEPTION_CATEGORY LIKE '%UW-BR- FTR:Bổ sung hồ sơ%' OR de.EXCEPTION_CATEGORY IN ('UW-BR-FTR: bổ sung hồ sơ','UW-BR-FTR:Giải trình, làm rõ nội dung hồ sơ trường hợp các nội dung yêu cầu giải trình làm rõ ngoài HD thẩm định'))) OR (de.ACTIVITYNAME = 'UnderwriterMaker' AND de.DECISION_CODE = 'Send_Back to BranchSupport' AND de.EXCEPTION_CATEGORY = 'UW-BR: Gửi dự thảo đề xuất cho chi nhánh') )) OR (kc.CUST_GROUP IN ('FDI','SOC','JSC','NBFI','BANK','STR') AND ( (de.ACTIVITYNAME = 'DetailDataEntry' AND de.DECISION_CODE = 'Send_Back' AND (de.EXCEPTION_CATEGORY LIKE 'DE-BR-NEW: Chất lượng bản scan mờ không thấy thông tin - %' OR de.EXCEPTION_CATEGORY IN ('DE-BR-NEW: Bổ sung ý kiến tư vấn của bên thứ 3 (pháp chế, chính sách, sản phẩm, thẩm định,…)','DE-BR-NEW: Lỗi hệ thống (LOS, T24, XHTD,…)','DE-BR-NEW: Lỗi lựa chọn phân luồng, quy trình trên hệ thống'))) OR (de.ACTIVITYNAME = 'DataInputerChecker' AND de.DECISION_CODE = 'Additional_Doc_Required' AND (de.EXCEPTION_CATEGORY LIKE 'BC3-BR-NEW: Chất lượng bản scan mờ không thấy thông tin - %' OR de.EXCEPTION_CATEGORY IN ('BC3-BR-NEW: Bổ sung ý kiến tư vấn của bên thứ 3 (pháp chế, chính sách, sản phẩm, thẩm định,…)','BC3-BR-NEW: Lỗi hệ thống (LOS, T24, XHTD,…)'))) OR (de.ACTIVITYNAME = 'UnderwriterMaker' AND de.DECISION_CODE = 'Additional_Doc_Required' AND (de.EXCEPTION_CATEGORY LIKE '%UW-BR- FTR:Bổ sung hồ sơ%' OR de.EXCEPTION_CATEGORY IN ('UW-BR-FTR: bổ sung hồ sơ','UW-BR-FTR:Giải trình, làm rõ nội dung hồ sơ trường hợp các nội dung yêu cầu giải trình làm rõ ngoài HD thẩm định','UW-BR: Gửi dự thảo đề xuất cho chi nhánh'))) )) ) AND EXISTS (SELECT 1 FROM C we LEFT JOIN D wd ON wd.DIMENSION_KEY = we.WORKSTEP_DECISION_SK WHERE we.WI_NAME = x.WI_NAME AND wd.WORKSTEP_CODE = de.ACTIVITYNAME AND wd.DECISION_CODE = de.DECISION_CODE)) THEN 'First Time Right' ELSE 'Not First Time Right' END</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="120" customHeight="1">
-      <c r="A32" s="28" t="inlineStr">
-        <is>
-          <t>FIRST_WORKSTEP_RETURN</t>
-        </is>
-      </c>
-      <c r="B32" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(200)</t>
-        </is>
-      </c>
-      <c r="C32" s="26" t="inlineStr">
-        <is>
-          <t>Bước trả về đầu tiên</t>
-        </is>
-      </c>
-      <c r="D32" s="54" t="inlineStr">
-        <is>
-          <t>Bước xử lý phát sinh trả về đầu tiên. WORKSTEP_CODE của dòng có MIN(EXITDATE) theo WI_NAME (không phải DAYID — WE là nhật ký toàn bộ lịch sử, không snapshot theo ngày) thỏa 3 nhánh OR về WORKSTEP_CODE/DECISION_CODE. DECISION_CODE tra qua WORKSTEP_DECISION_SK → STG_DIM_CLOS_WORKSTEP_DECISION</t>
-        </is>
-      </c>
-      <c r="E32" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT we.WORKSTEP_CODE FROM C we LEFT JOIN D wd ON wd.DIMENSION_KEY = we.WORKSTEP_DECISION_SK WHERE we.WI_NAME = A.WI_NAME AND we.EXITDATE IS NOT NULL AND ((we.WORKSTEP_CODE = 'DetailDataEntry' AND wd.DECISION_CODE = 'Send_Back') OR (we.WORKSTEP_CODE IN ('DataInputerChecker','UnderwriterMaker','CreditApproval') AND wd.DECISION_CODE = 'Additional_Doc_Required') OR (we.WORKSTEP_CODE = 'UnderwriterMaker' AND wd.DECISION_CODE = 'Send_Back to BranchSupport')) ORDER BY we.EXITDATE ASC FETCH FIRST 1 ROW ONLY)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="10" t="n"/>
-      <c r="B34" s="10" t="n"/>
-      <c r="C34" s="10" t="n"/>
-      <c r="D34" s="55" t="inlineStr">
+      <c r="C36" s="26" t="inlineStr">
+        <is>
+          <t>Phân loại lỗi nhập liệu</t>
+        </is>
+      </c>
+      <c r="D36" s="54" t="inlineStr">
+        <is>
+          <t>Phân loại nguyên nhân trả về ở khâu nhập liệu. C chỉ tồn tại vật lý ở PDTD_DTM (không có bản SB_DWH, xem hld/HLD_REF.md mục 2.4) — JOIN vào bảng REF_ là đặc quyền riêng của tầng PDTD_DTM.</t>
+        </is>
+      </c>
+      <c r="E36" s="31" t="inlineStr">
+        <is>
+          <t>C.PHAN_LOAI_DDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="10" t="n"/>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="55" t="inlineStr">
         <is>
           <t>Điều kiện join giữa các bảng</t>
         </is>
       </c>
-      <c r="E34" s="10" t="n"/>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="25" t="n"/>
-      <c r="B35" s="25" t="n"/>
-      <c r="C35" s="51" t="n"/>
-      <c r="D35" s="54" t="n"/>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t>LEFT JOIN B.EXCEPTION_CATEGORY = A.EXCEPTION_CATEGORY AND B.SYSTEMNAME = 'CLOS'</t>
+      <c r="E38" s="10" t="n"/>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="25" t="n"/>
+      <c r="B39" s="25" t="n"/>
+      <c r="C39" s="51" t="n"/>
+      <c r="D39" s="54" t="n"/>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN C.EXCEPTION_CATEGORY = A.EXCEPTION_CATEGORY AND C.SYSTEMNAME = 'CLOS'</t>
         </is>
       </c>
     </row>

--- a/mapping/PDTD_DTM/Mapping_FCT_CLOS_EXCEPTION.xlsx
+++ b/mapping/PDTD_DTM/Mapping_FCT_CLOS_EXCEPTION.xlsx
@@ -755,7 +755,7 @@
       </c>
       <c r="B2" s="19" t="inlineStr">
         <is>
-          <t>Bảng FACT chi tiết tại PDTD_DTM, bê nguyên 1:1 từ STG_DTM.STG_FCT_CLOS_EXCEPTION, bổ sung 3 cột phái sinh CHECK_FTR/FIRST_WORKSTEP_RETURN/PHAN_LOAI_DDE</t>
+          <t>Bảng FACT chi tiết tại PDTD_DTM, bê nguyên 1:1 từ STG_DTM.STG_FCT_CLOS_EXCEPTION, bổ sung 4 cột phái sinh WORKSTEP_CODE/CHECK_FTR/FIRST_WORKSTEP_RETURN/PHAN_LOAI_DDE</t>
         </is>
       </c>
       <c r="E2" s="52" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="E3" s="52" t="inlineStr">
         <is>
-          <t>REF_PHAN_LOAI_DDE AS C</t>
+          <t>STG_DIM_CLOS_EXCEPTION AS C</t>
         </is>
       </c>
     </row>
@@ -792,15 +792,27 @@
           <t>Chạy dữ liệu FULL hàng ngày</t>
         </is>
       </c>
-      <c r="E4" s="52" t="n"/>
+      <c r="E4" s="52" t="inlineStr">
+        <is>
+          <t>STG_DIM_CLOS_CUSTOMER AS D</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="n"/>
-      <c r="E5" s="52" t="n"/>
+      <c r="E5" s="52" t="inlineStr">
+        <is>
+          <t>STG_DIM_CLOS_WORKSTEP_DECISION AS E</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="13" t="n"/>
-      <c r="E6" s="52" t="n"/>
+      <c r="E6" s="52" t="inlineStr">
+        <is>
+          <t>REF_PHAN_LOAI_DDE AS F</t>
+        </is>
+      </c>
     </row>
     <row r="7" hidden="1">
       <c r="A7" s="13" t="n"/>
@@ -890,7 +902,7 @@
       </c>
       <c r="D17" s="54" t="inlineStr">
         <is>
-          <t>Ngày dữ liệu. Bê nguyên 1:1 từ SB_DWH (qua vùng chìa STG_DTM) cho các cột gốc.</t>
+          <t>PK (1/2) — Driving: STG_FCT_CLOS_EXCEPTION. Ngày dữ liệu. Bê nguyên 1:1 từ SB_DWH (qua vùng chìa STG_DTM) cho các cột gốc.</t>
         </is>
       </c>
       <c r="E17" s="31" t="inlineStr">
@@ -917,7 +929,7 @@
       </c>
       <c r="D18" s="54" t="inlineStr">
         <is>
-          <t>Khóa nghiệp vụ của dòng ngoại lệ, gộp WI_NAME+EXCEPTION_CATEGORY+RAISED_BY+RAISED_DATE_TIME</t>
+          <t>PK (2/2) — khóa nghiệp vụ của dòng ngoại lệ, gộp WI_NAME+EXCEPTION_CATEGORY+RAISED_BY+RAISED_DATE_TIME</t>
         </is>
       </c>
       <c r="E18" s="31" t="inlineStr">
@@ -980,10 +992,10 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
+    <row r="21" ht="45" customHeight="1">
       <c r="A21" s="28" t="inlineStr">
         <is>
-          <t>EXCEPTION_SK</t>
+          <t>USER_SK</t>
         </is>
       </c>
       <c r="B21" s="25" t="inlineStr">
@@ -993,186 +1005,186 @@
       </c>
       <c r="C21" s="26" t="inlineStr">
         <is>
-          <t>Khóa ngoại lệ</t>
+          <t>Khóa người nêu lý do</t>
         </is>
       </c>
       <c r="D21" s="54" t="inlineStr">
         <is>
-          <t>Khóa tới DIM_CLOS_EXCEPTION</t>
+          <t>Khóa tới DIM_LOS_USER, người nêu lý do (khớp naming convention DIM_LOS_USER.USER_SK đã dùng ở FCT_CLOS_WORKSTEP_EVENT)</t>
         </is>
       </c>
       <c r="E21" s="31" t="inlineStr">
         <is>
-          <t>A.EXCEPTION_SK</t>
+          <t>A.USER_SK</t>
         </is>
       </c>
     </row>
     <row r="22" ht="60" customHeight="1">
       <c r="A22" s="28" t="inlineStr">
         <is>
-          <t>WORKSTEP_CODE</t>
+          <t>USERNAME</t>
         </is>
       </c>
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(200)</t>
+          <t>VARCHAR2(150)</t>
         </is>
       </c>
       <c r="C22" s="26" t="inlineStr">
         <is>
-          <t>Mã bước xử lý ngoại lệ</t>
+          <t>Tên tài khoản người nêu</t>
         </is>
       </c>
       <c r="D22" s="54" t="inlineStr">
         <is>
-          <t>CỘT MỚI — BK cạnh SK, tương ứng ACTIVITYNAME của dòng DIM_CLOS_EXCEPTION đã khớp EXCEPTION_SK. Bê 1:1 từ SB_DWH (qua vùng chìa STG_DTM) — giá trị đã có sẵn trong bước lọc EXISTS tại SB_DWH, phục vụ truy vết/đối soát BK không qua DIM.</t>
+          <t>CỘT MỚI — BK cạnh SK, tên tài khoản dùng để lookup USER_SK, nguồn gốc xa NG_SB_CLOS_EXCEPTION.RAISED_BY (khác RAISED_BY, giữ tách biệt ý nghĩa khóa nghiệp vụ khỏi cột nghiệp vụ hiển thị)</t>
         </is>
       </c>
       <c r="E22" s="31" t="inlineStr">
         <is>
-          <t>A.WORKSTEP_CODE</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="60" customHeight="1">
+          <t>A.USERNAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
       <c r="A23" s="28" t="inlineStr">
         <is>
-          <t>DECISION_CODE</t>
+          <t>CUSTOMER_SK</t>
         </is>
       </c>
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(200)</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="C23" s="26" t="inlineStr">
         <is>
-          <t>Mã quyết định ngoại lệ</t>
+          <t>Khóa khách hàng</t>
         </is>
       </c>
       <c r="D23" s="54" t="inlineStr">
         <is>
-          <t>CỘT MỚI — nửa còn lại BK composite của DIM_CLOS_EXCEPTION ứng với dòng đã khớp EXCEPTION_SK. Bê 1:1 từ SB_DWH (qua vùng chìa STG_DTM) — giá trị đã có sẵn trong bước lọc EXISTS tại SB_DWH, phục vụ truy vết/đối soát BK không qua DIM.</t>
+          <t>Khóa tới DIM_CLOS_CUSTOMER</t>
         </is>
       </c>
       <c r="E23" s="31" t="inlineStr">
         <is>
-          <t>A.DECISION_CODE</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
+          <t>A.CUSTOMER_SK</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
       <c r="A24" s="28" t="inlineStr">
         <is>
-          <t>USER_SK</t>
+          <t>CUSTOMER_CODE</t>
         </is>
       </c>
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>VARCHAR2(100)</t>
         </is>
       </c>
       <c r="C24" s="26" t="inlineStr">
         <is>
-          <t>Khóa người nêu lý do</t>
+          <t>Mã khách hàng</t>
         </is>
       </c>
       <c r="D24" s="54" t="inlineStr">
         <is>
-          <t>Khóa tới DIM_LOS_USER, người nêu lý do</t>
+          <t>CỘT MỚI — BK cạnh SK, giá trị đã tra ra trong bước lookup CUSTOMER_SK tại SB_DWH</t>
         </is>
       </c>
       <c r="E24" s="31" t="inlineStr">
         <is>
-          <t>A.USER_SK</t>
+          <t>A.CUSTOMER_CODE</t>
         </is>
       </c>
     </row>
     <row r="25" ht="60" customHeight="1">
       <c r="A25" s="28" t="inlineStr">
         <is>
-          <t>USERNAME</t>
+          <t>EXCEPTION_CATEGORY</t>
         </is>
       </c>
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(150)</t>
+          <t>VARCHAR2(500)</t>
         </is>
       </c>
       <c r="C25" s="26" t="inlineStr">
         <is>
-          <t>Tên tài khoản người nêu</t>
+          <t>Phân nhóm nội dung</t>
         </is>
       </c>
       <c r="D25" s="54" t="inlineStr">
         <is>
-          <t>CỘT MỚI — BK cạnh SK, tên tài khoản dùng để lookup USER_SK. Bê 1:1 từ SB_DWH (qua vùng chìa STG_DTM), nguồn gốc xa NG_SB_CLOS_EXCEPTION.RAISED_BY — khác RAISED_BY (cột nghiệp vụ hiển thị), giữ tách biệt ý nghĩa khóa nghiệp vụ.</t>
+          <t>Phân nhóm nội dung cần làm rõ. Cũng là khóa JOIN sang REF_PHAN_LOAI_DDE (PHAN_LOAI_DDE) và STG_DIM_CLOS_EXCEPTION (WORKSTEP_CODE), và điều kiện whitelist miễn trừ khi tính CHECK_FTR</t>
         </is>
       </c>
       <c r="E25" s="31" t="inlineStr">
         <is>
-          <t>A.USERNAME</t>
+          <t>A.EXCEPTION_CATEGORY</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="28" t="inlineStr">
         <is>
-          <t>CUSTOMER_SK</t>
+          <t>RAISED_BY</t>
         </is>
       </c>
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>VARCHAR2(100)</t>
         </is>
       </c>
       <c r="C26" s="26" t="inlineStr">
         <is>
-          <t>Khóa khách hàng</t>
+          <t>Người nêu lý do</t>
         </is>
       </c>
       <c r="D26" s="54" t="inlineStr">
         <is>
-          <t>Khóa tới DIM_CLOS_CUSTOMER</t>
+          <t>Người nêu nội dung cần làm rõ</t>
         </is>
       </c>
       <c r="E26" s="31" t="inlineStr">
         <is>
-          <t>A.CUSTOMER_SK</t>
+          <t>A.RAISED_BY</t>
         </is>
       </c>
     </row>
     <row r="27" ht="45" customHeight="1">
       <c r="A27" s="28" t="inlineStr">
         <is>
-          <t>CUSTOMER_CODE</t>
+          <t>RAISED_DATE_TIME</t>
         </is>
       </c>
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(100)</t>
+          <t>TIMESTAMP</t>
         </is>
       </c>
       <c r="C27" s="26" t="inlineStr">
         <is>
-          <t>Mã khách hàng</t>
+          <t>Thời điểm nêu lý do</t>
         </is>
       </c>
       <c r="D27" s="54" t="inlineStr">
         <is>
-          <t>CỘT MỚI — BK cạnh SK, giá trị đã tra ra trong bước lookup CUSTOMER_SK. Bê 1:1 từ SB_DWH (qua vùng chìa STG_DTM), phục vụ truy vết/đối soát BK không qua DIM.</t>
+          <t>Thời điểm nêu nội dung cần làm rõ, đồng thời là nguồn tính PROCESSED_DATE (TRUNC ở tầng report) và điều kiện gating khi tính WORKSTEP_CODE</t>
         </is>
       </c>
       <c r="E27" s="31" t="inlineStr">
         <is>
-          <t>A.CUSTOMER_CODE</t>
+          <t>A.RAISED_DATE_TIME</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="28" t="inlineStr">
         <is>
-          <t>EXCEPTION_CATEGORY</t>
+          <t>EXCEPTION_NAME</t>
         </is>
       </c>
       <c r="B28" s="25" t="inlineStr">
@@ -1182,246 +1194,214 @@
       </c>
       <c r="C28" s="26" t="inlineStr">
         <is>
-          <t>Phân nhóm nội dung</t>
+          <t>Tên nội dung ngoại lệ</t>
         </is>
       </c>
       <c r="D28" s="54" t="inlineStr">
         <is>
-          <t>Phân nhóm nội dung cần làm rõ</t>
+          <t>Tên nội dung cần làm rõ</t>
         </is>
       </c>
       <c r="E28" s="31" t="inlineStr">
         <is>
-          <t>A.EXCEPTION_CATEGORY</t>
+          <t>A.EXCEPTION_NAME</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="28" t="inlineStr">
         <is>
-          <t>RAISED_BY</t>
+          <t>EXCEPTION_REMARKS</t>
         </is>
       </c>
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(100)</t>
+          <t>VARCHAR2(4000)</t>
         </is>
       </c>
       <c r="C29" s="26" t="inlineStr">
         <is>
-          <t>Người nêu lý do</t>
+          <t>Ghi chú ngoại lệ</t>
         </is>
       </c>
       <c r="D29" s="54" t="inlineStr">
         <is>
-          <t>Người nêu nội dung cần làm rõ</t>
+          <t>Ghi chú của nội dung cần làm rõ</t>
         </is>
       </c>
       <c r="E29" s="31" t="inlineStr">
         <is>
-          <t>A.RAISED_BY</t>
+          <t>A.EXCEPTION_REMARKS</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="28" t="inlineStr">
         <is>
-          <t>RAISED_DATE_TIME</t>
+          <t>RCTYPE</t>
         </is>
       </c>
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>VARCHAR2(20)</t>
         </is>
       </c>
       <c r="C30" s="26" t="inlineStr">
         <is>
-          <t>Thời điểm nêu lý do</t>
+          <t>Loại ghi nhận</t>
         </is>
       </c>
       <c r="D30" s="54" t="inlineStr">
         <is>
-          <t>Thời điểm nêu nội dung cần làm rõ</t>
+          <t>Loại ghi nhận, Raise hay Clear</t>
         </is>
       </c>
       <c r="E30" s="31" t="inlineStr">
         <is>
-          <t>A.RAISED_DATE_TIME</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
+          <t>A.RCTYPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="165" customHeight="1">
       <c r="A31" s="28" t="inlineStr">
         <is>
-          <t>EXCEPTION_NAME</t>
+          <t>WORKSTEP_CODE</t>
         </is>
       </c>
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(500)</t>
+          <t>VARCHAR2(200)</t>
         </is>
       </c>
       <c r="C31" s="26" t="inlineStr">
         <is>
-          <t>Tên nội dung ngoại lệ</t>
+          <t>Bước xử lý ngoại lệ</t>
         </is>
       </c>
       <c r="D31" s="54" t="inlineStr">
         <is>
-          <t>Tên nội dung cần làm rõ</t>
+          <t>Bước xử lý tương ứng ngoại lệ — ĐỔI TÊN từ ACTIVITYNAME (SRS BC7), PHÁI SINH TẠI PDTD_DTM (SRS BC7 cập nhật 2026-10-28), thay thế hoàn toàn logic EXCEPTION_SK/WORKSTEP_CODE/DECISION_CODE cũ (đã xóa khỏi SB_DWH). Join B (gating: bước DetailDataEntry+Submit sớm nhất theo WI_NAME, điều kiện RAISED_DATE_TIME&gt;=ENTRYDATE) không lấy giá trị; join C theo EXCEPTION_CATEGORY (không còn EXCEPTION_NAME) mới là nguồn giá trị ACTIVITYNAME. Mặc định NULL nếu không khớp. Alias CLOS xác nhận với BA: SRS gốc ghi nhầm 'NG_SB_RLOS_MAS_EXCEPTION' ở nhánh CLOS — lỗi chính tả, đúng phải là CLOS.</t>
         </is>
       </c>
       <c r="E31" s="31" t="inlineStr">
         <is>
-          <t>A.EXCEPTION_NAME</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1">
+          <t>C.ACTIVITYNAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="375" customHeight="1">
       <c r="A32" s="28" t="inlineStr">
         <is>
-          <t>EXCEPTION_REMARKS</t>
+          <t>CHECK_FTR</t>
         </is>
       </c>
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(4000)</t>
+          <t>VARCHAR2(20)</t>
         </is>
       </c>
       <c r="C32" s="26" t="inlineStr">
         <is>
-          <t>Ghi chú ngoại lệ</t>
+          <t>Vi phạm First Time Right</t>
         </is>
       </c>
       <c r="D32" s="54" t="inlineStr">
         <is>
-          <t>Ghi chú của nội dung cần làm rõ</t>
+          <t>Vi phạm nguyên tắc First Time Right — per-hồ-sơ (mọi dòng cùng WI_NAME phải cùng đạt điều kiện). SRS BC7 cập nhật 2026-10-28: ĐÃ GIẢN LƯỢC, bỏ phân nhánh theo WORKSTEP/DECISION và EXISTS qua WORKSTEP_EVENT của logic cũ — chỉ còn xét theo CUST_GROUP (tra qua CUSTOMER_SK) + EXCEPTION_CATEGORY (dùng trực tiếp, không cần join DIM_CLOS_EXCEPTION). Nhóm KHDN (MSME/SME/USME) và nhóm KHDNL/ĐT&amp;ĐCTC (FDI/SOC/JSC/NBFI/BANK/STR) dùng chung 1 danh sách EXCEPTION_CATEGORY miễn trừ. Đây là giản lược nghiệp vụ đáng kể — đã xác nhận với BA.</t>
         </is>
       </c>
       <c r="E32" s="31" t="inlineStr">
         <is>
-          <t>A.EXCEPTION_REMARKS</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1">
+          <t>CASE WHEN NOT EXISTS (SELECT 1 FROM STG_FCT_CLOS_EXCEPTION x LEFT JOIN STG_DIM_CLOS_CUSTOMER kc ON kc.DIMENSION_KEY = x.CUSTOMER_SK WHERE x.WI_NAME = A.WI_NAME AND NOT ( (kc.CUST_GROUP IN ('MSME','SME','USME') AND (x.EXCEPTION_CATEGORY LIKE N'%DE-BR-NEW: Chất lượng bản scan mờ không thấy thông tin - %' OR x.EXCEPTION_CATEGORY IN (N'DE-BR-NEW: Bổ sung ý kiến tư vấn của bên thứ 3 (pháp chế, chính sách, sản phẩm, thẩm định,…)', N'DE-BR-NEW: Lỗi hệ thống (LOS, T24, XHTD,…)', N'DE-BR-NEW: Lỗi lựa chọn phân luồng, quy trình trên hệ thống', N'BC3-BR-NEW: Bổ sung ý kiến tư vấn của bên thứ 3 (pháp chế, chính sách, sản phẩm, thẩm định,…)', N'BC3-BR-NEW: Lỗi hệ thống (LOS, T24, XHTD,…)', N'UW-BR-FTR: bổ sung hồ sơ', N'UW-BR-FTR:Giải trình, làm rõ nội dung hồ sơ trường hợp các nội dung yêu cầu giải trình làm rõ ngoài HD thẩm định', N'UW-BR: Gửi dự thảo đề xuất cho chi nhánh') OR x.EXCEPTION_CATEGORY LIKE N'%BC3-BR-NEW: Chất lượng bản scan mờ không thấy thông tin - %' OR x.EXCEPTION_CATEGORY LIKE N'%UW-BR- FTR:Bổ sung hồ sơ%')) OR (kc.CUST_GROUP IN ('FDI','SOC','JSC','NBFI','BANK','STR') AND (x.EXCEPTION_CATEGORY LIKE N'%DE-BR-NEW: Chất lượng bản scan mờ không thấy thông tin - %' OR x.EXCEPTION_CATEGORY IN (N'DE-BR-NEW: Bổ sung ý kiến tư vấn của bên thứ 3 (pháp chế, chính sách, sản phẩm, thẩm định,…)', N'DE-BR-NEW: Lỗi hệ thống (LOS, T24, XHTD,…)', N'DE-BR-NEW: Lỗi lựa chọn phân luồng, quy trình trên hệ thống', N'BC3-BR-NEW: Bổ sung ý kiến tư vấn của bên thứ 3 (pháp chế, chính sách, sản phẩm, thẩm định,…)', N'BC3-BR-NEW: Lỗi hệ thống (LOS, T24, XHTD,…)', N'UW-BR-FTR: bổ sung hồ sơ', N'UW-BR-FTR:Giải trình, làm rõ nội dung hồ sơ trường hợp các nội dung yêu cầu giải trình làm rõ ngoài HD thẩm định', N'UW-BR: Gửi dự thảo đề xuất cho chi nhánh') OR x.EXCEPTION_CATEGORY LIKE N'%BC3-BR-NEW: Chất lượng bản scan mờ không thấy thông tin - %' OR x.EXCEPTION_CATEGORY LIKE N'%UW-BR- FTR:Bổ sung hồ sơ%')) )) THEN 'First Time Right' ELSE 'Not First Time Right' END</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="135" customHeight="1">
       <c r="A33" s="28" t="inlineStr">
         <is>
-          <t>RCTYPE</t>
+          <t>FIRST_WORKSTEP_RETURN</t>
         </is>
       </c>
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(20)</t>
+          <t>VARCHAR2(200)</t>
         </is>
       </c>
       <c r="C33" s="26" t="inlineStr">
         <is>
-          <t>Loại ghi nhận</t>
+          <t>Bước trả về đầu tiên</t>
         </is>
       </c>
       <c r="D33" s="54" t="inlineStr">
         <is>
-          <t>Loại ghi nhận, Raise hay Clear</t>
+          <t>Bước xử lý phát sinh trả về đầu tiên. WORKSTEP_CODE của dòng có MIN(EXITDATE) theo WI_NAME (không phải DAYID — WE là nhật ký toàn bộ lịch sử, không snapshot theo ngày) thỏa 3 nhánh OR về WORKSTEP_CODE/DECISION_CODE. DECISION_CODE tra qua WORKSTEP_DECISION_SK → STG_DIM_CLOS_WORKSTEP_DECISION (đi qua vùng chìa STG_DTM; WE không denormalize DECISION_CODE).</t>
         </is>
       </c>
       <c r="E33" s="31" t="inlineStr">
         <is>
-          <t>A.RCTYPE</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="285" customHeight="1">
+          <t>(SELECT B.WORKSTEP_CODE FROM STG_FCT_CLOS_WORKSTEP_EVENT B LEFT JOIN STG_DIM_CLOS_WORKSTEP_DECISION E ON E.DIMENSION_KEY = B.WORKSTEP_DECISION_SK WHERE B.WI_NAME = A.WI_NAME AND B.EXITDATE IS NOT NULL AND ((B.WORKSTEP_CODE = 'DetailDataEntry' AND E.DECISION_CODE = 'Send_Back') OR (B.WORKSTEP_CODE IN ('DataInputerChecker','UnderwriterMaker','CreditApproval') AND E.DECISION_CODE = 'Additional_Doc_Required') OR (B.WORKSTEP_CODE = 'UnderwriterMaker' AND E.DECISION_CODE = 'Send_Back to BranchSupport')) ORDER BY B.EXITDATE ASC FETCH FIRST 1 ROW ONLY)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="45" customHeight="1">
       <c r="A34" s="28" t="inlineStr">
         <is>
-          <t>CHECK_FTR</t>
+          <t>PHAN_LOAI_DDE</t>
         </is>
       </c>
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(20)</t>
+          <t>VARCHAR2(100)</t>
         </is>
       </c>
       <c r="C34" s="26" t="inlineStr">
         <is>
-          <t>Vi phạm First Time Right</t>
+          <t>Phân loại lỗi nhập liệu</t>
         </is>
       </c>
       <c r="D34" s="54" t="inlineStr">
         <is>
-          <t>Vi phạm nguyên tắc First Time Right — per-hồ-sơ (mọi dòng cùng WI_NAME phải cùng đạt điều kiện). Đọc nguyên văn SRS BC7 BR 1.2/1.3 bảng T8 row 12 'CHECK_FTR' nhánh CLOS: logic SRS định nghĩa 'trường hợp NGOẠI LỆ hợp lệ' theo tổ hợp ACTIVITYNAME+DECISION_CODE+EXCEPTION_CATEGORY cụ thể, phân theo CUST_GROUP (KHDN/KHDNL), và tổ hợp WORKSTEP/DECISION đó phải thực sự tồn tại trong lịch sử xử lý (EXISTS STG_FCT_CLOS_WORKSTEP_EVENT).</t>
+          <t>Phân loại nguyên nhân trả về ở khâu nhập liệu. F chỉ tồn tại vật lý ở PDTD_DTM (không có bản SB_DWH, xem hld/HLD_REF.md mục 2.4) — JOIN vào bảng REF_ là đặc quyền riêng của tầng PDTD_DTM.</t>
         </is>
       </c>
       <c r="E34" s="31" t="inlineStr">
         <is>
-          <t>CASE WHEN NOT EXISTS (SELECT 1 FROM STG_FCT_CLOS_EXCEPTION x LEFT JOIN STG_DIM_CLOS_EXCEPTION de ON de.DIMENSION_KEY = x.EXCEPTION_SK LEFT JOIN STG_DIM_CLOS_CUSTOMER kc ON kc.DIMENSION_KEY = x.CUSTOMER_SK WHERE x.WI_NAME = A.WI_NAME AND NOT ( ( (kc.CUST_GROUP IN ('MSME','SME','USME') AND ( (de.ACTIVITYNAME = 'DetailDataEntry' AND de.DECISION_CODE = 'Send_Back' AND (de.EXCEPTION_CATEGORY LIKE 'DE-BR-NEW: ...' OR de.EXCEPTION_CATEGORY IN (...))) OR (de.ACTIVITYNAME = 'DataInputerChecker' AND de.DECISION_CODE = 'Additional_Doc_Required' AND (...)) OR (de.ACTIVITYNAME = 'UnderwriterMaker' AND de.DECISION_CODE = 'Additional_Doc_Required' AND (...)) OR (de.ACTIVITYNAME = 'UnderwriterMaker' AND de.DECISION_CODE = 'Send_Back to BranchSupport' AND de.EXCEPTION_CATEGORY = 'UW-BR: Gửi dự thảo đề xuất cho chi nhánh') )) OR (kc.CUST_GROUP IN ('FDI','SOC','JSC','NBFI','BANK','STR') AND (...cùng 3 tổ hợp đầu, không có tổ hợp Send_Back to BranchSupport riêng...)) ) ) AND EXISTS (SELECT 1 FROM STG_FCT_CLOS_WORKSTEP_EVENT we LEFT JOIN STG_DIM_CLOS_WORKSTEP_DECISION wd ON wd.DIMENSION_KEY = we.WORKSTEP_DECISION_SK WHERE we.WI_NAME = x.WI_NAME AND wd.WORKSTEP_CODE = de.ACTIVITYNAME AND wd.DECISION_CODE = de.DECISION_CODE)) THEN 'First Time Right' ELSE 'Not First Time Right' END</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="135" customHeight="1">
-      <c r="A35" s="28" t="inlineStr">
-        <is>
-          <t>FIRST_WORKSTEP_RETURN</t>
-        </is>
-      </c>
-      <c r="B35" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(200)</t>
-        </is>
-      </c>
-      <c r="C35" s="26" t="inlineStr">
-        <is>
-          <t>Bước trả về đầu tiên</t>
-        </is>
-      </c>
-      <c r="D35" s="54" t="inlineStr">
-        <is>
-          <t>Bước xử lý phát sinh trả về đầu tiên. WORKSTEP_CODE của dòng có MIN(EXITDATE) theo WI_NAME (không phải DAYID — WE là nhật ký toàn bộ lịch sử, không snapshot theo ngày) thỏa 3 nhánh OR về WORKSTEP_CODE/DECISION_CODE. DECISION_CODE tra qua WORKSTEP_DECISION_SK → STG_DIM_CLOS_WORKSTEP_DECISION (đi qua vùng chìa STG_DTM; WE không denormalize DECISION_CODE).</t>
-        </is>
-      </c>
-      <c r="E35" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT we.WORKSTEP_CODE FROM STG_FCT_CLOS_WORKSTEP_EVENT we LEFT JOIN STG_DIM_CLOS_WORKSTEP_DECISION wd ON wd.DIMENSION_KEY = we.WORKSTEP_DECISION_SK WHERE we.WI_NAME = A.WI_NAME AND we.EXITDATE IS NOT NULL AND ((we.WORKSTEP_CODE = 'DetailDataEntry' AND wd.DECISION_CODE = 'Send_Back') OR (we.WORKSTEP_CODE IN ('DataInputerChecker','UnderwriterMaker','CreditApproval') AND wd.DECISION_CODE = 'Additional_Doc_Required') OR (we.WORKSTEP_CODE = 'UnderwriterMaker' AND wd.DECISION_CODE = 'Send_Back to BranchSupport')) ORDER BY we.EXITDATE ASC FETCH FIRST 1 ROW ONLY)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="45" customHeight="1">
-      <c r="A36" s="28" t="inlineStr">
-        <is>
-          <t>PHAN_LOAI_DDE</t>
-        </is>
-      </c>
-      <c r="B36" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(100)</t>
-        </is>
-      </c>
-      <c r="C36" s="26" t="inlineStr">
-        <is>
-          <t>Phân loại lỗi nhập liệu</t>
-        </is>
-      </c>
-      <c r="D36" s="54" t="inlineStr">
-        <is>
-          <t>Phân loại nguyên nhân trả về ở khâu nhập liệu. C chỉ tồn tại vật lý ở PDTD_DTM (không có bản SB_DWH, xem hld/HLD_REF.md mục 2.4) — JOIN vào bảng REF_ là đặc quyền riêng của tầng PDTD_DTM.</t>
-        </is>
-      </c>
-      <c r="E36" s="31" t="inlineStr">
-        <is>
-          <t>C.PHAN_LOAI_DDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="10" t="n"/>
-      <c r="B38" s="10" t="n"/>
-      <c r="C38" s="10" t="n"/>
-      <c r="D38" s="55" t="inlineStr">
+          <t>F.PHAN_LOAI_DDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="10" t="n"/>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="55" t="inlineStr">
         <is>
           <t>Điều kiện join giữa các bảng</t>
         </is>
       </c>
-      <c r="E38" s="10" t="n"/>
+      <c r="E36" s="10" t="n"/>
+    </row>
+    <row r="37" ht="75" customHeight="1">
+      <c r="A37" s="25" t="n"/>
+      <c r="B37" s="25" t="n"/>
+      <c r="C37" s="51" t="n"/>
+      <c r="D37" s="54" t="n"/>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN (SELECT we.*, ROW_NUMBER() OVER (PARTITION BY WI_NAME ORDER BY ENTRYDATE ASC) RN FROM STG_FCT_CLOS_WORKSTEP_EVENT we WHERE we.WORKSTEP_CODE = 'DetailDataEntry' AND we.DECISION_CODE = 'Submit') B ON B.WI_NAME = A.WI_NAME AND B.RN = 1 AND TRUNC(A.RAISED_DATE_TIME) &gt;= TRUNC(B.ENTRYDATE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" s="25" t="n"/>
+      <c r="B38" s="25" t="n"/>
+      <c r="C38" s="51" t="n"/>
+      <c r="D38" s="54" t="n"/>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN (SELECT DISTINCT ACTIVITYNAME, EXCEPTION_CATEGORY FROM STG_DIM_CLOS_EXCEPTION WHERE EXP_DATE IS NULL AND ACTIVITYNAME IN ('DetailDataEntry','DataInputerChecker','UnderwriterMaker','UnderwriterChecker','CreditApproval','CreditCommittee')) C ON C.EXCEPTION_CATEGORY = A.EXCEPTION_CATEGORY</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="25" t="n"/>
@@ -1430,7 +1410,7 @@
       <c r="D39" s="54" t="n"/>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>LEFT JOIN C.EXCEPTION_CATEGORY = A.EXCEPTION_CATEGORY AND C.SYSTEMNAME = 'CLOS'</t>
+          <t>LEFT JOIN F.EXCEPTION_CATEGORY = A.EXCEPTION_CATEGORY AND F.SYSTEMNAME = 'CLOS'</t>
         </is>
       </c>
     </row>
